--- a/results_cnn_subnetwork_evaluation/PLV_subnetwork_separate_node_index/summary_plv_separate_node.xlsx
+++ b/results_cnn_subnetwork_evaluation/PLV_subnetwork_separate_node_index/summary_plv_separate_node.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71668188-6E54-42BB-8C9D-DF1D9DA6A3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="633" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="633" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plv_separate_nodes" sheetId="13" r:id="rId1"/>
@@ -2413,17 +2413,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2499,6 +2499,76 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:H4">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
@@ -2509,26 +2579,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -2539,79 +2589,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:H12">
+    <cfRule type="colorScale" priority="1047">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1046">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="1045">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1046">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1047">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2791,17 +2791,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2837,6 +2837,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:L6">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -2847,29 +2857,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:L12">
+    <cfRule type="colorScale" priority="1054">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="1053">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1054">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2893,17 +2893,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:L19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2937,17 +2937,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:R21">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5245,17 +5245,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5379,77 +5379,77 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5483,6 +5483,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:H4">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
@@ -5523,6 +5533,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -5543,27 +5563,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5585,6 +5585,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -5595,29 +5605,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:H23 C3:H6">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5821,17 +5821,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5889,17 +5889,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:L15">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5923,17 +5923,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29:L30">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5989,17 +5989,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32:R32">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7775,17 +7775,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:B11">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7919,6 +7919,46 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:H2">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -7939,26 +7979,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -7989,28 +8009,48 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:H4">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
@@ -8021,77 +8061,37 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8135,17 +8135,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:H17 A13:H13 C3:H3 A5:H8">
+    <cfRule type="colorScale" priority="572">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="571">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="572">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8383,17 +8383,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8451,6 +8451,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:L10 K12:L12">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -8461,18 +8471,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:L11">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -8483,18 +8493,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14:L15 K17:L17">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -8505,29 +8515,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:L16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8551,17 +8551,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:L24">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11558,17 +11558,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:A35">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11640,6 +11640,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:H4">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -11651,56 +11701,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11732,27 +11732,27 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="255">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="254">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="253">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="254">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="255">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11812,17 +11812,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:I26">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11846,6 +11846,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J4">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -11866,26 +11916,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -11897,36 +11927,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11984,17 +11984,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12040,17 +12040,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
